--- a/data/trans_camb/P36B08_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P36B08_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40,71</t>
+          <t>42,09</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,03</t>
+          <t>39,06</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>39,4</t>
+          <t>40,62</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 8,22</t>
+          <t>-5,15; 8,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 18,72</t>
+          <t>5,18; 17,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,52; 46,98</t>
+          <t>35,87; 47,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 17,56</t>
+          <t>4,34; 17,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 16,44</t>
+          <t>3,48; 16,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,15; 44,08</t>
+          <t>32,77; 44,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 10,8</t>
+          <t>1,39; 10,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 15,61</t>
+          <t>6,23; 15,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,62; 44,03</t>
+          <t>36,11; 44,53</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>79,11%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 18,02</t>
+          <t>-9,58; 17,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,91; 41,07</t>
+          <t>9,96; 37,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,59; 101,07</t>
+          <t>68,04; 103,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,77; 35,6</t>
+          <t>7,32; 34,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,92; 32,87</t>
+          <t>6,25; 33,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,65; 90,26</t>
+          <t>59,38; 91,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 21,91</t>
+          <t>2,61; 21,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,92; 31,78</t>
+          <t>11,5; 31,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65,19; 90,6</t>
+          <t>66,92; 91,45</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32,91</t>
+          <t>32,5</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,65</t>
+          <t>26,36</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>30,11</t>
+          <t>29,73</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 10,42</t>
+          <t>0,17; 10,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 11,76</t>
+          <t>1,36; 11,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,28; 37,87</t>
+          <t>28,08; 37,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 11,32</t>
+          <t>1,76; 11,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 8,41</t>
+          <t>-1,62; 8,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,51; 31,41</t>
+          <t>22,65; 31,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 9,54</t>
+          <t>2,32; 9,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 8,64</t>
+          <t>1,52; 8,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,9; 33,19</t>
+          <t>26,43; 32,63</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 17,46</t>
+          <t>0,24; 17,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 19,84</t>
+          <t>2,15; 19,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,63; 65,16</t>
+          <t>43,18; 63,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 17,21</t>
+          <t>2,47; 17,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 12,88</t>
+          <t>-2,3; 12,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,25; 48,17</t>
+          <t>31,64; 48,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 15,0</t>
+          <t>3,47; 15,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 13,52</t>
+          <t>2,14; 13,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40,15; 52,99</t>
+          <t>39,34; 52,0</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32,48</t>
+          <t>32,9</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,53</t>
+          <t>23,94</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27,8</t>
+          <t>28,21</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,63; 17,26</t>
+          <t>6,66; 17,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,65; 15,04</t>
+          <t>4,62; 14,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27,92; 36,71</t>
+          <t>28,2; 37,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,91; 13,27</t>
+          <t>4,28; 13,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,51</t>
+          <t>1,1; 10,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,81; 27,2</t>
+          <t>20,39; 27,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,57; 13,91</t>
+          <t>6,71; 13,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 10,82</t>
+          <t>3,88; 11,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,04; 30,67</t>
+          <t>25,21; 31,09</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,28; 29,51</t>
+          <t>10,36; 29,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,15; 25,78</t>
+          <t>7,08; 24,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43,08; 63,88</t>
+          <t>42,9; 63,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,3; 19,06</t>
+          <t>5,43; 19,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 14,96</t>
+          <t>1,52; 15,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,09; 39,21</t>
+          <t>27,02; 40,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,5; 21,45</t>
+          <t>9,87; 21,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,79; 16,56</t>
+          <t>5,58; 17,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36,06; 47,53</t>
+          <t>36,38; 48,04</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31,65</t>
+          <t>30,51</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,22</t>
+          <t>19,05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25,44</t>
+          <t>24,82</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 13,38</t>
+          <t>2,59; 14,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 12,37</t>
+          <t>0,59; 12,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,42; 37,24</t>
+          <t>25,26; 34,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 10,95</t>
+          <t>1,28; 11,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 7,49</t>
+          <t>-1,81; 7,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,13; 22,71</t>
+          <t>15,15; 23,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 10,96</t>
+          <t>3,15; 10,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 8,86</t>
+          <t>1,32; 8,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,53; 28,65</t>
+          <t>21,95; 27,98</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,67; 21,55</t>
+          <t>4,09; 23,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,5; 20,06</t>
+          <t>0,88; 20,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40,11; 60,79</t>
+          <t>37,08; 57,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,1; 14,77</t>
+          <t>1,64; 15,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 10,08</t>
+          <t>-2,33; 10,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,75; 30,86</t>
+          <t>18,87; 31,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,19; 15,88</t>
+          <t>4,34; 15,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,73; 13,1</t>
+          <t>1,72; 12,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,71; 41,89</t>
+          <t>29,91; 40,99</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22,84</t>
+          <t>23,29</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,98</t>
+          <t>22,05</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>22,35</t>
+          <t>22,63</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 13,32</t>
+          <t>0,07; 12,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,2; 13,39</t>
+          <t>2,0; 14,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,73; 28,09</t>
+          <t>18,2; 28,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,46; 13,72</t>
+          <t>2,27; 13,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,93; 14,45</t>
+          <t>2,64; 13,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,62; 26,3</t>
+          <t>17,38; 26,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,1; 11,62</t>
+          <t>3,47; 11,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,92; 12,09</t>
+          <t>4,29; 12,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,11; 25,59</t>
+          <t>18,82; 25,78</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,88; 19,95</t>
+          <t>0,14; 19,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1,65; 19,99</t>
+          <t>3,02; 21,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23,66; 42,23</t>
+          <t>24,17; 42,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3,25; 19,55</t>
+          <t>2,92; 18,82</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,9; 20,59</t>
+          <t>3,39; 19,63</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,43; 37,6</t>
+          <t>22,01; 37,31</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,03; 16,64</t>
+          <t>4,67; 16,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5,22; 17,14</t>
+          <t>5,76; 17,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>25,54; 37,38</t>
+          <t>24,79; 37,06</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22,62</t>
+          <t>22,53</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,68</t>
+          <t>18,43</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21,25</t>
+          <t>20,29</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,44; 16,26</t>
+          <t>2,77; 16,39</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,25; 15,36</t>
+          <t>1,19; 14,16</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17,52; 27,95</t>
+          <t>17,45; 28,04</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,93; 14,78</t>
+          <t>4,47; 14,76</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,68; 12,06</t>
+          <t>0,5; 11,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,36; 24,6</t>
+          <t>14,24; 23,17</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,29; 13,73</t>
+          <t>4,9; 13,9</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,92; 11,49</t>
+          <t>3,23; 11,75</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18,17; 25,33</t>
+          <t>16,87; 23,8</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3,21; 23,8</t>
+          <t>3,67; 23,94</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1,59; 22,43</t>
+          <t>1,57; 20,67</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22,85; 41,72</t>
+          <t>22,91; 41,94</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4,81; 19,88</t>
+          <t>5,57; 19,9</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,85; 16,29</t>
+          <t>0,63; 16,08</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,86; 33,31</t>
+          <t>17,6; 31,47</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,73; 18,82</t>
+          <t>6,34; 18,98</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3,8; 15,75</t>
+          <t>4,15; 16,36</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>23,11; 35,05</t>
+          <t>21,51; 32,8</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21,05</t>
+          <t>21,16</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,49</t>
+          <t>18,66</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>19,49</t>
+          <t>19,63</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,01; 17,59</t>
+          <t>1,65; 16,82</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,49; 14,79</t>
+          <t>0,2; 14,54</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14,93; 27,13</t>
+          <t>15,0; 26,92</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,18; 14,11</t>
+          <t>2,01; 13,61</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 8,44</t>
+          <t>-4,67; 8,69</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,67; 23,74</t>
+          <t>13,72; 23,81</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,6; 13,23</t>
+          <t>2,96; 12,74</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 9,08</t>
+          <t>-1,09; 9,15</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15,4; 23,47</t>
+          <t>15,83; 23,51</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2,59; 25,08</t>
+          <t>2,43; 24,02</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,65; 21,03</t>
+          <t>0,08; 20,13</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18,36; 38,9</t>
+          <t>18,38; 38,57</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2,81; 19,42</t>
+          <t>2,48; 18,4</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 11,53</t>
+          <t>-5,84; 11,57</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,66; 32,89</t>
+          <t>16,78; 32,64</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,63; 18,06</t>
+          <t>3,71; 17,23</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 12,35</t>
+          <t>-1,41; 12,48</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>19,23; 32,37</t>
+          <t>19,86; 32,32</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31,2</t>
+          <t>31,14</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,82</t>
+          <t>24,65</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>27,97</t>
+          <t>27,85</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,38</t>
+          <t>5,5; 10,13</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>6,87; 11,44</t>
+          <t>6,89; 11,68</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>29,28; 33,31</t>
+          <t>28,99; 33,02</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6,16; 10,49</t>
+          <t>6,31; 10,38</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>4,31; 8,41</t>
+          <t>3,95; 8,23</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>23,11; 26,45</t>
+          <t>22,95; 26,3</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,55; 9,7</t>
+          <t>6,61; 9,82</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,29</t>
+          <t>6,0; 9,19</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>26,62; 29,41</t>
+          <t>26,63; 29,11</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>8,67; 16,76</t>
+          <t>8,57; 16,44</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>10,68; 18,54</t>
+          <t>10,57; 18,67</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>45,2; 53,98</t>
+          <t>44,77; 53,67</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8,59; 14,97</t>
+          <t>8,67; 14,8</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>5,96; 12,01</t>
+          <t>5,5; 11,85</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>31,92; 37,86</t>
+          <t>31,67; 37,77</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,72; 14,62</t>
+          <t>9,72; 14,82</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>8,92; 14,04</t>
+          <t>8,85; 13,94</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>39,09; 44,47</t>
+          <t>39,03; 44,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P36B08_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P36B08_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales]</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
